--- a/apps/api/data/CarbonCo_ESG_Social.xlsx
+++ b/apps/api/data/CarbonCo_ESG_Social.xlsx
@@ -20,8 +20,59 @@
     <sheet name="ESRS_G1" sheetId="12" state="visible" r:id="rId12"/>
     <sheet name="Claude Log" sheetId="13" state="visible" r:id="rId13"/>
     <sheet name="ESRS_Simplifie" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="_Manifest" sheetId="15" state="visible" r:id="rId15"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="CC_VSME_BP1_Raison_Sociale">'VSME_Reporting'!$D$7</definedName>
+    <definedName name="CC_VSME_BP2_Secteur_NAF">'VSME_Reporting'!$D$8</definedName>
+    <definedName name="CC_VSME_BP3_ETP">'VSME_Reporting'!$D$9</definedName>
+    <definedName name="CC_VSME_BP4_CA_Net">'VSME_Reporting'!$D$10</definedName>
+    <definedName name="CC_VSME_BP5_Annee">'VSME_Reporting'!$D$11</definedName>
+    <definedName name="CC_VSME_BP6_Pays">'VSME_Reporting'!$D$12</definedName>
+    <definedName name="CC_VSME_BP7_Perimetre">'VSME_Reporting'!$D$13</definedName>
+    <definedName name="CC_VSME_E1_Scope1">'VSME_Reporting'!$D$17</definedName>
+    <definedName name="CC_VSME_E2_Scope2_LB">'VSME_Reporting'!$D$18</definedName>
+    <definedName name="CC_VSME_E3_Scope2_MB">'VSME_Reporting'!$D$19</definedName>
+    <definedName name="CC_VSME_E4_Scope3">'VSME_Reporting'!$D$20</definedName>
+    <definedName name="CC_VSME_E5_Total_GES">'VSME_Reporting'!$D$21</definedName>
+    <definedName name="CC_VSME_E6_Intensite_CA">'VSME_Reporting'!$D$22</definedName>
+    <definedName name="CC_VSME_E7_Energie_MWh">'VSME_Reporting'!$D$23</definedName>
+    <definedName name="CC_VSME_E8_Part_ENR">'VSME_Reporting'!$D$24</definedName>
+    <definedName name="CC_VSME_E9_Eau_m3">'VSME_Reporting'!$D$25</definedName>
+    <definedName name="CC_VSME_E10_Dechets_t">'VSME_Reporting'!$D$26</definedName>
+    <definedName name="CC_VSME_E11_Valorisation_Pct">'VSME_Reporting'!$D$27</definedName>
+    <definedName name="CC_VSME_E12_Plan_GES">'VSME_Reporting'!$D$28</definedName>
+    <definedName name="CC_VSME_S1_Effectif">'VSME_Reporting'!$D$32</definedName>
+    <definedName name="CC_VSME_S2_Pct_CDI">'VSME_Reporting'!$D$33</definedName>
+    <definedName name="CC_VSME_S3_Rotation_Pct">'VSME_Reporting'!$D$34</definedName>
+    <definedName name="CC_VSME_S4_LTIR">'VSME_Reporting'!$D$35</definedName>
+    <definedName name="CC_VSME_S5_Formation_h_ETP">'VSME_Reporting'!$D$36</definedName>
+    <definedName name="CC_VSME_S6_Ecart_Salaire_HF">'VSME_Reporting'!$D$37</definedName>
+    <definedName name="CC_VSME_S7_Pct_Femmes_Mgmt">'VSME_Reporting'!$D$38</definedName>
+    <definedName name="CC_VSME_S8_Diversite">'VSME_Reporting'!$D$39</definedName>
+    <definedName name="CC_VSME_S9_Dialogue_Social">'VSME_Reporting'!$D$40</definedName>
+    <definedName name="CC_VSME_S10_Litiges">'VSME_Reporting'!$D$41</definedName>
+    <definedName name="CC_VSME_G1_Anti_Corruption">'VSME_Reporting'!$D$45</definedName>
+    <definedName name="CC_VSME_G2_Formation_Ethique">'VSME_Reporting'!$D$46</definedName>
+    <definedName name="CC_VSME_G3_Whistleblowing">'VSME_Reporting'!$D$47</definedName>
+    <definedName name="CC_VSME_G4_Pct_CA_Independants">'VSME_Reporting'!$D$48</definedName>
+    <definedName name="CC_VSME_G5_Protection_Donnees">'VSME_Reporting'!$D$49</definedName>
+    <definedName name="CC_MAT_E1_Score_Impact">'Materialite'!$F$10</definedName>
+    <definedName name="CC_MAT_E2_Score_Impact">'Materialite'!$F$11</definedName>
+    <definedName name="CC_MAT_E3_Score_Impact">'Materialite'!$F$12</definedName>
+    <definedName name="CC_MAT_E4_Score_Impact">'Materialite'!$F$13</definedName>
+    <definedName name="CC_MAT_E5_Score_Impact">'Materialite'!$F$14</definedName>
+    <definedName name="CC_MAT_S1_Score_Impact">'Materialite'!$F$15</definedName>
+    <definedName name="CC_MAT_S2_Score_Impact">'Materialite'!$F$16</definedName>
+    <definedName name="CC_MAT_S3_Score_Impact">'Materialite'!$F$17</definedName>
+    <definedName name="CC_MAT_S4_Score_Impact">'Materialite'!$F$18</definedName>
+    <definedName name="CC_MAT_G1_Score_Impact">'Materialite'!$F$19</definedName>
+    <definedName name="CC_ESG_Score_Global">'Synthese_ESG'!$D$10</definedName>
+    <definedName name="CC_ESG_Score_E">'Synthese_ESG'!$D$6</definedName>
+    <definedName name="CC_ESG_Score_S">'Synthese_ESG'!$D$7</definedName>
+    <definedName name="CC_ESG_Score_G">'Synthese_ESG'!$D$8</definedName>
+    <definedName name="CC_ESG_Enjeux_Materiels">'Synthese_ESG'!$D$16</definedName>
+  </definedNames>
   <calcPr calcId="191029" fullCalcOnLoad="1" iterateDelta="0.0001"/>
 </workbook>
 </file>
@@ -5479,6 +5530,87 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>CarbonCo_ESG_Social — Manifest</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Version</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2026-04-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Onglets obligatoires</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Couverture,Sommaire,Liaison_Donnees,VSME_Reporting,Materialite,Synthese_ESG,ESRS_S1,Controles_QC_ESG,Claude Log</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Plages CC_* requises</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Controles QC</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
